--- a/División/RUC_División.xlsx
+++ b/División/RUC_División.xlsx
@@ -428,16 +428,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>42.33910482161736</v>
+        <v>42.33910482161738</v>
       </c>
       <c r="C2" s="2">
-        <v>115.2076323450615</v>
+        <v>115.1895201239744</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>48.77788022107912</v>
+        <v>48.77021166880757</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -445,7 +445,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>22.76920128936084</v>
+        <v>22.76920128936085</v>
       </c>
       <c r="C3" s="2">
         <v>109.3726525833701</v>
